--- a/t_analysis/神火股份_000933.SZ抓取数据_T策略分析.xlsx
+++ b/t_analysis/神火股份_000933.SZ抓取数据_T策略分析.xlsx
@@ -558,16 +558,16 @@
         </is>
       </c>
       <c r="C2" s="3">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D2" s="3">
         <v>251</v>
       </c>
       <c r="E2" s="3">
-        <v>54.3</v>
+        <v>54.4</v>
       </c>
       <c r="F2" s="3">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -602,16 +602,16 @@
         </is>
       </c>
       <c r="C4" s="3">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D4" s="3">
         <v>212</v>
       </c>
       <c r="E4" s="3">
-        <v>53.3</v>
+        <v>53.4</v>
       </c>
       <c r="F4" s="3">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -646,16 +646,16 @@
         </is>
       </c>
       <c r="C6" s="3">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D6" s="3">
         <v>159</v>
       </c>
       <c r="E6" s="3">
-        <v>52.1</v>
+        <v>52.3</v>
       </c>
       <c r="F6" s="3">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -690,16 +690,16 @@
         </is>
       </c>
       <c r="C8" s="3">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D8" s="3">
         <v>137</v>
       </c>
       <c r="E8" s="3">
-        <v>54.2</v>
+        <v>54.4</v>
       </c>
       <c r="F8" s="3">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -892,16 +892,16 @@
         </is>
       </c>
       <c r="C3" s="3">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="D3" s="3">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E3" s="3">
-        <v>42.1</v>
+        <v>42.0</v>
       </c>
       <c r="F3" s="3">
-        <v>6.5</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -936,16 +936,16 @@
         </is>
       </c>
       <c r="C5" s="3">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="D5" s="3">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E5" s="3">
         <v>42.2</v>
       </c>
       <c r="F5" s="3">
-        <v>6.43</v>
+        <v>6.46</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -980,16 +980,16 @@
         </is>
       </c>
       <c r="C7" s="3">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="D7" s="3">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E7" s="3">
-        <v>42.8</v>
+        <v>42.7</v>
       </c>
       <c r="F7" s="3">
-        <v>6.27</v>
+        <v>6.31</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1024,16 +1024,16 @@
         </is>
       </c>
       <c r="C9" s="3">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="D9" s="3">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E9" s="3">
-        <v>42.7</v>
+        <v>42.6</v>
       </c>
       <c r="F9" s="3">
-        <v>6.43</v>
+        <v>6.47</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1068,16 +1068,16 @@
         </is>
       </c>
       <c r="C11" s="3">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="D11" s="3">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E11" s="3">
-        <v>42.8</v>
+        <v>42.7</v>
       </c>
       <c r="F11" s="3">
-        <v>6.71</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1112,16 +1112,16 @@
         </is>
       </c>
       <c r="C13" s="3">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D13" s="3">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E13" s="3">
-        <v>44.9</v>
+        <v>44.8</v>
       </c>
       <c r="F13" s="3">
-        <v>6.47</v>
+        <v>6.52</v>
       </c>
     </row>
   </sheetData>
@@ -1292,14 +1292,14 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E6" s="3">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="F6" s="3">
-        <v>60.4</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1318,14 +1318,14 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E7" s="3">
-        <v>333</v>
+        <v>101</v>
       </c>
       <c r="F7" s="3">
-        <v>48.6</v>
+        <v>60.4</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1344,14 +1344,14 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E8" s="3">
-        <v>61</v>
+        <v>332</v>
       </c>
       <c r="F8" s="3">
-        <v>41.0</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1362,22 +1362,22 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C9" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E9" s="3">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="F9" s="3">
-        <v>66.7</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1396,14 +1396,14 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E10" s="3">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="F10" s="3">
-        <v>46.4</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1422,14 +1422,14 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E11" s="3">
-        <v>175</v>
+        <v>28</v>
       </c>
       <c r="F11" s="3">
-        <v>43.4</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1448,14 +1448,14 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E12" s="3">
-        <v>61</v>
+        <v>175</v>
       </c>
       <c r="F12" s="3">
-        <v>60.7</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C13" s="3">
@@ -1474,14 +1474,14 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E13" s="3">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="F13" s="3">
-        <v>61.4</v>
+        <v>60.7</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1500,14 +1500,14 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E14" s="3">
-        <v>245</v>
+        <v>83</v>
       </c>
       <c r="F14" s="3">
-        <v>49.0</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1526,14 +1526,14 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E15" s="3">
-        <v>34</v>
+        <v>245</v>
       </c>
       <c r="F15" s="3">
-        <v>44.1</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1544,22 +1544,22 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C16" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E16" s="3">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F16" s="3">
-        <v>53.3</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1578,14 +1578,14 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E17" s="3">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="F17" s="3">
-        <v>39.8</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -1604,14 +1604,14 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E18" s="3">
-        <v>22</v>
+        <v>93</v>
       </c>
       <c r="F18" s="3">
-        <v>40.9</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C19" s="3">
@@ -1630,14 +1630,14 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E19" s="3">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="F19" s="3">
-        <v>67.2</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1656,14 +1656,14 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E20" s="3">
-        <v>140</v>
+        <v>61</v>
       </c>
       <c r="F20" s="3">
-        <v>48.6</v>
+        <v>67.2</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1682,14 +1682,14 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E21" s="3">
-        <v>14</v>
+        <v>140</v>
       </c>
       <c r="F21" s="3">
-        <v>42.9</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -1700,22 +1700,22 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C22" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E22" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F22" s="3">
-        <v>58.3</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -1734,14 +1734,14 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E23" s="3">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="F23" s="3">
-        <v>35.3</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -1760,14 +1760,14 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E24" s="3">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="F24" s="3">
-        <v>35.7</v>
+        <v>35.3</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C25" s="3">
@@ -1786,14 +1786,14 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E25" s="3">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="F25" s="3">
-        <v>68.8</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -1812,14 +1812,14 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E26" s="3">
-        <v>93</v>
+        <v>48</v>
       </c>
       <c r="F26" s="3">
-        <v>52.7</v>
+        <v>68.8</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -1838,14 +1838,14 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E27" s="3">
-        <v>9</v>
+        <v>93</v>
       </c>
       <c r="F27" s="3">
-        <v>44.4</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -1856,22 +1856,22 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C28" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E28" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F28" s="3">
-        <v>40.0</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -1890,14 +1890,14 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E29" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F29" s="3">
-        <v>30.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -1916,14 +1916,14 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E30" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F30" s="3">
-        <v>0.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C31" s="3">
@@ -1942,14 +1942,14 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E31" s="3">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="F31" s="3">
-        <v>55.6</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -1968,14 +1968,14 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E32" s="3">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="F32" s="3">
-        <v>45.0</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -1994,14 +1994,14 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E33" s="3">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="F33" s="3">
-        <v>0.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -2012,15 +2012,15 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C34" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E34" s="3">
@@ -2046,14 +2046,14 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E35" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F35" s="3">
-        <v>33.3</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -2072,14 +2072,14 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E36" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F36" s="3">
-        <v>0.0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C37" s="3">
@@ -2098,14 +2098,14 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E37" s="3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F37" s="3">
-        <v>66.7</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -2124,14 +2124,14 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E38" s="3">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F38" s="3">
-        <v>37.5</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -2150,40 +2150,40 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E39" s="3">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F39" s="3">
-        <v>0.0</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>10日</t>
+          <t>5日</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C40" s="3">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E40" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F40" s="3">
-        <v>11.1</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -2202,14 +2202,14 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E41" s="3">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="F41" s="3">
-        <v>73.3</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -2228,14 +2228,14 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E42" s="3">
-        <v>292</v>
+        <v>30</v>
       </c>
       <c r="F42" s="3">
-        <v>54.5</v>
+        <v>73.3</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -2254,14 +2254,14 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E43" s="3">
-        <v>128</v>
+        <v>292</v>
       </c>
       <c r="F43" s="3">
-        <v>57.8</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C44" s="3">
@@ -2280,14 +2280,14 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E44" s="3">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="F44" s="3">
-        <v>100.0</v>
+        <v>57.8</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -2306,14 +2306,14 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E45" s="3">
-        <v>103</v>
+        <v>3</v>
       </c>
       <c r="F45" s="3">
-        <v>69.9</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -2332,14 +2332,14 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E46" s="3">
-        <v>433</v>
+        <v>103</v>
       </c>
       <c r="F46" s="3">
-        <v>46.9</v>
+        <v>69.9</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -2358,14 +2358,14 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E47" s="3">
-        <v>85</v>
+        <v>432</v>
       </c>
       <c r="F47" s="3">
-        <v>40.0</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -2376,22 +2376,22 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C48" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E48" s="3">
-        <v>7</v>
+        <v>85</v>
       </c>
       <c r="F48" s="3">
-        <v>14.3</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -2410,14 +2410,14 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E49" s="3">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="F49" s="3">
-        <v>72.7</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -2436,14 +2436,14 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E50" s="3">
-        <v>226</v>
+        <v>22</v>
       </c>
       <c r="F50" s="3">
-        <v>54.4</v>
+        <v>72.7</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -2462,14 +2462,14 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E51" s="3">
-        <v>95</v>
+        <v>226</v>
       </c>
       <c r="F51" s="3">
-        <v>51.6</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C52" s="3">
@@ -2488,14 +2488,14 @@
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E52" s="3">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c r="F52" s="3">
-        <v>100.0</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -2514,14 +2514,14 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E53" s="3">
-        <v>93</v>
+        <v>2</v>
       </c>
       <c r="F53" s="3">
-        <v>68.8</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -2540,14 +2540,14 @@
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E54" s="3">
-        <v>356</v>
+        <v>93</v>
       </c>
       <c r="F54" s="3">
-        <v>48.0</v>
+        <v>68.8</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -2566,14 +2566,14 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E55" s="3">
-        <v>52</v>
+        <v>355</v>
       </c>
       <c r="F55" s="3">
-        <v>42.3</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -2584,22 +2584,22 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C56" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E56" s="3">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="F56" s="3">
-        <v>0.0</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -2618,14 +2618,14 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E57" s="3">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="F57" s="3">
-        <v>70.6</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -2644,14 +2644,14 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E58" s="3">
-        <v>145</v>
+        <v>17</v>
       </c>
       <c r="F58" s="3">
-        <v>52.4</v>
+        <v>70.6</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -2670,14 +2670,14 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E59" s="3">
-        <v>53</v>
+        <v>145</v>
       </c>
       <c r="F59" s="3">
-        <v>58.5</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C60" s="3">
@@ -2696,14 +2696,14 @@
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E60" s="3">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="F60" s="3">
-        <v>100.0</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -2722,14 +2722,14 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E61" s="3">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="F61" s="3">
-        <v>70.4</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -2748,14 +2748,14 @@
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E62" s="3">
-        <v>241</v>
+        <v>71</v>
       </c>
       <c r="F62" s="3">
-        <v>49.0</v>
+        <v>70.4</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -2774,14 +2774,14 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E63" s="3">
-        <v>33</v>
+        <v>240</v>
       </c>
       <c r="F63" s="3">
-        <v>42.4</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -2792,22 +2792,22 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C64" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E64" s="3">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="F64" s="3">
-        <v>84.6</v>
+        <v>42.4</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -2826,14 +2826,14 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E65" s="3">
-        <v>111</v>
+        <v>13</v>
       </c>
       <c r="F65" s="3">
-        <v>54.1</v>
+        <v>84.6</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -2852,14 +2852,14 @@
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E66" s="3">
-        <v>37</v>
+        <v>111</v>
       </c>
       <c r="F66" s="3">
-        <v>64.9</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C67" s="3">
@@ -2878,14 +2878,14 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E67" s="3">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="F67" s="3">
-        <v>68.3</v>
+        <v>64.9</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -2904,14 +2904,14 @@
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E68" s="3">
-        <v>194</v>
+        <v>1</v>
       </c>
       <c r="F68" s="3">
-        <v>47.4</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -2930,14 +2930,14 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E69" s="3">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="F69" s="3">
-        <v>39.1</v>
+        <v>68.3</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -2948,22 +2948,22 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C70" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E70" s="3">
-        <v>6</v>
+        <v>193</v>
       </c>
       <c r="F70" s="3">
-        <v>66.7</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -2974,22 +2974,22 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C71" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E71" s="3">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="F71" s="3">
-        <v>51.0</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -3008,14 +3008,14 @@
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E72" s="3">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F72" s="3">
-        <v>50.0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C73" s="3">
@@ -3034,14 +3034,14 @@
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E73" s="3">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="F73" s="3">
-        <v>63.6</v>
+        <v>51.0</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C74" s="3">
@@ -3060,14 +3060,14 @@
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E74" s="3">
-        <v>96</v>
+        <v>12</v>
       </c>
       <c r="F74" s="3">
-        <v>51.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -3086,14 +3086,14 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E75" s="3">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F75" s="3">
-        <v>50.0</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -3104,22 +3104,22 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C76" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E76" s="3">
-        <v>2</v>
+        <v>96</v>
       </c>
       <c r="F76" s="3">
-        <v>0.0</v>
+        <v>51.0</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -3130,22 +3130,22 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C77" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E77" s="3">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F77" s="3">
-        <v>57.1</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -3164,14 +3164,14 @@
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E78" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F78" s="3">
-        <v>66.7</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -3182,7 +3182,7 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C79" s="3">
@@ -3190,14 +3190,14 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E79" s="3">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F79" s="3">
-        <v>68.4</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C80" s="3">
@@ -3216,14 +3216,14 @@
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E80" s="3">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="F80" s="3">
-        <v>57.5</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -3242,66 +3242,66 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E81" s="3">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F81" s="3">
-        <v>25.0</v>
+        <v>68.4</v>
       </c>
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>20日</t>
+          <t>10日</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C82" s="3">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E82" s="3">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F82" s="3">
-        <v>61.9</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>20日</t>
+          <t>10日</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C83" s="3">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E83" s="3">
-        <v>313</v>
+        <v>4</v>
       </c>
       <c r="F83" s="3">
-        <v>54.6</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -3320,14 +3320,14 @@
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E84" s="3">
-        <v>111</v>
+        <v>42</v>
       </c>
       <c r="F84" s="3">
-        <v>63.1</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C85" s="3">
@@ -3346,14 +3346,14 @@
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E85" s="3">
-        <v>9</v>
+        <v>313</v>
       </c>
       <c r="F85" s="3">
-        <v>100.0</v>
+        <v>54.6</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C86" s="3">
@@ -3372,14 +3372,14 @@
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E86" s="3">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="F86" s="3">
-        <v>55.9</v>
+        <v>63.1</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -3398,14 +3398,14 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E87" s="3">
-        <v>465</v>
+        <v>9</v>
       </c>
       <c r="F87" s="3">
-        <v>46.2</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -3424,14 +3424,14 @@
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E88" s="3">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="F88" s="3">
-        <v>28.7</v>
+        <v>55.9</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -3442,22 +3442,22 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C89" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E89" s="3">
-        <v>34</v>
+        <v>464</v>
       </c>
       <c r="F89" s="3">
-        <v>70.6</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -3468,22 +3468,22 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C90" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E90" s="3">
-        <v>256</v>
+        <v>129</v>
       </c>
       <c r="F90" s="3">
-        <v>55.5</v>
+        <v>28.7</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -3502,14 +3502,14 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E91" s="3">
-        <v>90</v>
+        <v>34</v>
       </c>
       <c r="F91" s="3">
-        <v>61.1</v>
+        <v>70.6</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C92" s="3">
@@ -3528,14 +3528,14 @@
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E92" s="3">
-        <v>7</v>
+        <v>256</v>
       </c>
       <c r="F92" s="3">
-        <v>100.0</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C93" s="3">
@@ -3554,14 +3554,14 @@
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E93" s="3">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="F93" s="3">
-        <v>56.8</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="94" spans="1:6">
@@ -3580,14 +3580,14 @@
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E94" s="3">
-        <v>417</v>
+        <v>8</v>
       </c>
       <c r="F94" s="3">
-        <v>46.5</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -3606,14 +3606,14 @@
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E95" s="3">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F95" s="3">
-        <v>33.0</v>
+        <v>56.8</v>
       </c>
     </row>
     <row r="96" spans="1:6">
@@ -3624,22 +3624,22 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C96" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E96" s="3">
-        <v>25</v>
+        <v>416</v>
       </c>
       <c r="F96" s="3">
-        <v>68.0</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -3650,22 +3650,22 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C97" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E97" s="3">
-        <v>188</v>
+        <v>100</v>
       </c>
       <c r="F97" s="3">
-        <v>53.7</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="98" spans="1:6">
@@ -3684,14 +3684,14 @@
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E98" s="3">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="F98" s="3">
-        <v>64.2</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="99" spans="1:6">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C99" s="3">
@@ -3710,14 +3710,14 @@
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E99" s="3">
-        <v>5</v>
+        <v>188</v>
       </c>
       <c r="F99" s="3">
-        <v>100.0</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="100" spans="1:6">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C100" s="3">
@@ -3736,14 +3736,14 @@
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E100" s="3">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="F100" s="3">
-        <v>59.0</v>
+        <v>64.2</v>
       </c>
     </row>
     <row r="101" spans="1:6">
@@ -3762,14 +3762,14 @@
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E101" s="3">
-        <v>350</v>
+        <v>6</v>
       </c>
       <c r="F101" s="3">
-        <v>46.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="102" spans="1:6">
@@ -3788,14 +3788,14 @@
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E102" s="3">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="F102" s="3">
-        <v>36.4</v>
+        <v>59.0</v>
       </c>
     </row>
     <row r="103" spans="1:6">
@@ -3806,22 +3806,22 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C103" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E103" s="3">
-        <v>20</v>
+        <v>349</v>
       </c>
       <c r="F103" s="3">
-        <v>65.0</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="104" spans="1:6">
@@ -3832,22 +3832,22 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C104" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E104" s="3">
-        <v>145</v>
+        <v>66</v>
       </c>
       <c r="F104" s="3">
-        <v>57.2</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="105" spans="1:6">
@@ -3866,14 +3866,14 @@
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E105" s="3">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="F105" s="3">
-        <v>73.9</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="106" spans="1:6">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C106" s="3">
@@ -3892,14 +3892,14 @@
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E106" s="3">
-        <v>4</v>
+        <v>145</v>
       </c>
       <c r="F106" s="3">
-        <v>100.0</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="107" spans="1:6">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C107" s="3">
@@ -3918,14 +3918,14 @@
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E107" s="3">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="F107" s="3">
-        <v>59.7</v>
+        <v>73.9</v>
       </c>
     </row>
     <row r="108" spans="1:6">
@@ -3944,14 +3944,14 @@
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E108" s="3">
-        <v>303</v>
+        <v>4</v>
       </c>
       <c r="F108" s="3">
-        <v>47.2</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="109" spans="1:6">
@@ -3970,14 +3970,14 @@
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E109" s="3">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="F109" s="3">
-        <v>34.0</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="110" spans="1:6">
@@ -3988,22 +3988,22 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C110" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E110" s="3">
-        <v>9</v>
+        <v>303</v>
       </c>
       <c r="F110" s="3">
-        <v>66.7</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="111" spans="1:6">
@@ -4014,22 +4014,22 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C111" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E111" s="3">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="F111" s="3">
-        <v>52.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="112" spans="1:6">
@@ -4048,14 +4048,14 @@
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E112" s="3">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="F112" s="3">
-        <v>83.3</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C113" s="3">
@@ -4074,14 +4074,14 @@
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E113" s="3">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F113" s="3">
-        <v>66.7</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C114" s="3">
@@ -4100,14 +4100,14 @@
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E114" s="3">
-        <v>207</v>
+        <v>30</v>
       </c>
       <c r="F114" s="3">
-        <v>44.4</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -4126,14 +4126,14 @@
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E115" s="3">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="F115" s="3">
-        <v>29.6</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="116" spans="1:6">
@@ -4144,22 +4144,22 @@
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C116" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E116" s="3">
-        <v>3</v>
+        <v>207</v>
       </c>
       <c r="F116" s="3">
-        <v>100.0</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -4170,22 +4170,22 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C117" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E117" s="3">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F117" s="3">
-        <v>38.5</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -4204,14 +4204,14 @@
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E118" s="3">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F118" s="3">
-        <v>83.3</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="119" spans="1:6">
@@ -4222,7 +4222,7 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C119" s="3">
@@ -4230,14 +4230,14 @@
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E119" s="3">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="F119" s="3">
-        <v>75.9</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -4248,7 +4248,7 @@
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C120" s="3">
@@ -4256,14 +4256,14 @@
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E120" s="3">
-        <v>134</v>
+        <v>12</v>
       </c>
       <c r="F120" s="3">
-        <v>45.5</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -4282,66 +4282,66 @@
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E121" s="3">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F121" s="3">
-        <v>33.3</v>
+        <v>75.9</v>
       </c>
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>30日</t>
+          <t>20日</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C122" s="3">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E122" s="3">
-        <v>5</v>
+        <v>134</v>
       </c>
       <c r="F122" s="3">
-        <v>0.0</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>30日</t>
+          <t>20日</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C123" s="3">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E123" s="3">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="F123" s="3">
-        <v>52.6</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -4360,14 +4360,14 @@
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E124" s="3">
-        <v>314</v>
+        <v>5</v>
       </c>
       <c r="F124" s="3">
-        <v>51.6</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="125" spans="1:6">
@@ -4386,14 +4386,14 @@
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E125" s="3">
-        <v>105</v>
+        <v>38</v>
       </c>
       <c r="F125" s="3">
-        <v>65.7</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C126" s="3">
@@ -4412,14 +4412,14 @@
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E126" s="3">
-        <v>112</v>
+        <v>313</v>
       </c>
       <c r="F126" s="3">
-        <v>57.1</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C127" s="3">
@@ -4438,14 +4438,14 @@
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E127" s="3">
-        <v>523</v>
+        <v>105</v>
       </c>
       <c r="F127" s="3">
-        <v>44.0</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -4464,14 +4464,14 @@
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E128" s="3">
-        <v>145</v>
+        <v>112</v>
       </c>
       <c r="F128" s="3">
-        <v>24.1</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -4482,22 +4482,22 @@
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C129" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E129" s="3">
-        <v>3</v>
+        <v>523</v>
       </c>
       <c r="F129" s="3">
-        <v>0.0</v>
+        <v>44.0</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -4508,22 +4508,22 @@
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C130" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E130" s="3">
-        <v>27</v>
+        <v>145</v>
       </c>
       <c r="F130" s="3">
-        <v>40.7</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -4542,14 +4542,14 @@
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E131" s="3">
-        <v>270</v>
+        <v>2</v>
       </c>
       <c r="F131" s="3">
-        <v>50.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -4568,14 +4568,14 @@
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E132" s="3">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="F132" s="3">
-        <v>67.3</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C133" s="3">
@@ -4594,14 +4594,14 @@
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E133" s="3">
-        <v>106</v>
+        <v>270</v>
       </c>
       <c r="F133" s="3">
-        <v>58.5</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="134" spans="1:6">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C134" s="3">
@@ -4620,14 +4620,14 @@
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E134" s="3">
-        <v>479</v>
+        <v>98</v>
       </c>
       <c r="F134" s="3">
-        <v>44.1</v>
+        <v>67.3</v>
       </c>
     </row>
     <row r="135" spans="1:6">
@@ -4646,14 +4646,14 @@
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E135" s="3">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="F135" s="3">
-        <v>22.3</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -4664,22 +4664,22 @@
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C136" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E136" s="3">
-        <v>3</v>
+        <v>479</v>
       </c>
       <c r="F136" s="3">
-        <v>0.0</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -4690,22 +4690,22 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C137" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E137" s="3">
-        <v>23</v>
+        <v>121</v>
       </c>
       <c r="F137" s="3">
-        <v>43.5</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -4724,14 +4724,14 @@
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E138" s="3">
-        <v>205</v>
+        <v>2</v>
       </c>
       <c r="F138" s="3">
-        <v>48.3</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -4750,14 +4750,14 @@
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E139" s="3">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="F139" s="3">
-        <v>67.6</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C140" s="3">
@@ -4776,14 +4776,14 @@
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E140" s="3">
-        <v>98</v>
+        <v>205</v>
       </c>
       <c r="F140" s="3">
-        <v>58.2</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C141" s="3">
@@ -4802,14 +4802,14 @@
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E141" s="3">
-        <v>405</v>
+        <v>74</v>
       </c>
       <c r="F141" s="3">
-        <v>45.7</v>
+        <v>67.6</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -4828,14 +4828,14 @@
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E142" s="3">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F142" s="3">
-        <v>20.6</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -4846,22 +4846,22 @@
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C143" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E143" s="3">
-        <v>1</v>
+        <v>405</v>
       </c>
       <c r="F143" s="3">
-        <v>0.0</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -4872,22 +4872,22 @@
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C144" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E144" s="3">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="F144" s="3">
-        <v>38.1</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -4906,14 +4906,14 @@
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E145" s="3">
-        <v>165</v>
+        <v>21</v>
       </c>
       <c r="F145" s="3">
-        <v>50.3</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="146" spans="1:6">
@@ -4932,14 +4932,14 @@
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E146" s="3">
-        <v>66</v>
+        <v>165</v>
       </c>
       <c r="F146" s="3">
-        <v>69.7</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C147" s="3">
@@ -4958,14 +4958,14 @@
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E147" s="3">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="F147" s="3">
-        <v>62.2</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="148" spans="1:6">
@@ -4984,14 +4984,14 @@
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E148" s="3">
-        <v>351</v>
+        <v>90</v>
       </c>
       <c r="F148" s="3">
-        <v>45.9</v>
+        <v>62.2</v>
       </c>
     </row>
     <row r="149" spans="1:6">
@@ -5010,14 +5010,14 @@
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E149" s="3">
-        <v>73</v>
+        <v>351</v>
       </c>
       <c r="F149" s="3">
-        <v>21.9</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="150" spans="1:6">
@@ -5028,22 +5028,22 @@
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C150" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E150" s="3">
-        <v>14</v>
+        <v>73</v>
       </c>
       <c r="F150" s="3">
-        <v>42.9</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="151" spans="1:6">
@@ -5062,14 +5062,14 @@
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E151" s="3">
-        <v>98</v>
+        <v>14</v>
       </c>
       <c r="F151" s="3">
-        <v>46.9</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="152" spans="1:6">
@@ -5088,14 +5088,14 @@
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E152" s="3">
-        <v>41</v>
+        <v>98</v>
       </c>
       <c r="F152" s="3">
-        <v>73.2</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="153" spans="1:6">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C153" s="3">
@@ -5114,14 +5114,14 @@
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E153" s="3">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="F153" s="3">
-        <v>65.7</v>
+        <v>73.2</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -5140,14 +5140,14 @@
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E154" s="3">
-        <v>259</v>
+        <v>67</v>
       </c>
       <c r="F154" s="3">
-        <v>49.0</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="155" spans="1:6">
@@ -5166,14 +5166,14 @@
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E155" s="3">
-        <v>42</v>
+        <v>259</v>
       </c>
       <c r="F155" s="3">
-        <v>21.4</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="156" spans="1:6">
@@ -5184,22 +5184,22 @@
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C156" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E156" s="3">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="F156" s="3">
-        <v>50.0</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="157" spans="1:6">
@@ -5218,14 +5218,14 @@
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E157" s="3">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="F157" s="3">
-        <v>41.1</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="158" spans="1:6">
@@ -5244,14 +5244,14 @@
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E158" s="3">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="F158" s="3">
-        <v>78.3</v>
+        <v>41.1</v>
       </c>
     </row>
     <row r="159" spans="1:6">
@@ -5262,7 +5262,7 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C159" s="3">
@@ -5270,14 +5270,14 @@
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E159" s="3">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="F159" s="3">
-        <v>62.7</v>
+        <v>78.3</v>
       </c>
     </row>
     <row r="160" spans="1:6">
@@ -5296,14 +5296,14 @@
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E160" s="3">
-        <v>194</v>
+        <v>51</v>
       </c>
       <c r="F160" s="3">
-        <v>47.4</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="161" spans="1:6">
@@ -5322,40 +5322,40 @@
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E161" s="3">
-        <v>26</v>
+        <v>194</v>
       </c>
       <c r="F161" s="3">
-        <v>15.4</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>90日</t>
+          <t>30日</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C162" s="3">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E162" s="3">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="F162" s="3">
-        <v>77.5</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="163" spans="1:6">
@@ -5374,14 +5374,14 @@
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E163" s="3">
-        <v>226</v>
+        <v>40</v>
       </c>
       <c r="F163" s="3">
-        <v>77.4</v>
+        <v>77.5</v>
       </c>
     </row>
     <row r="164" spans="1:6">
@@ -5400,14 +5400,14 @@
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E164" s="3">
-        <v>84</v>
+        <v>226</v>
       </c>
       <c r="F164" s="3">
-        <v>95.2</v>
+        <v>77.4</v>
       </c>
     </row>
     <row r="165" spans="1:6">
@@ -5418,7 +5418,7 @@
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C165" s="3">
@@ -5426,14 +5426,14 @@
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E165" s="3">
-        <v>116</v>
+        <v>84</v>
       </c>
       <c r="F165" s="3">
-        <v>50.9</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="166" spans="1:6">
@@ -5452,14 +5452,14 @@
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E166" s="3">
-        <v>598</v>
+        <v>116</v>
       </c>
       <c r="F166" s="3">
-        <v>43.3</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="167" spans="1:6">
@@ -5478,14 +5478,14 @@
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E167" s="3">
-        <v>184</v>
+        <v>597</v>
       </c>
       <c r="F167" s="3">
-        <v>32.6</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -5496,22 +5496,22 @@
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C168" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E168" s="3">
-        <v>38</v>
+        <v>184</v>
       </c>
       <c r="F168" s="3">
-        <v>78.9</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="169" spans="1:6">
@@ -5530,14 +5530,14 @@
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E169" s="3">
-        <v>196</v>
+        <v>38</v>
       </c>
       <c r="F169" s="3">
-        <v>79.6</v>
+        <v>78.9</v>
       </c>
     </row>
     <row r="170" spans="1:6">
@@ -5556,14 +5556,14 @@
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E170" s="3">
-        <v>76</v>
+        <v>196</v>
       </c>
       <c r="F170" s="3">
-        <v>94.7</v>
+        <v>79.6</v>
       </c>
     </row>
     <row r="171" spans="1:6">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C171" s="3">
@@ -5582,14 +5582,14 @@
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E171" s="3">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="F171" s="3">
-        <v>52.2</v>
+        <v>94.7</v>
       </c>
     </row>
     <row r="172" spans="1:6">
@@ -5608,14 +5608,14 @@
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E172" s="3">
-        <v>579</v>
+        <v>113</v>
       </c>
       <c r="F172" s="3">
-        <v>43.4</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="173" spans="1:6">
@@ -5634,14 +5634,14 @@
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E173" s="3">
-        <v>177</v>
+        <v>578</v>
       </c>
       <c r="F173" s="3">
-        <v>32.2</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="174" spans="1:6">
@@ -5652,22 +5652,22 @@
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C174" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E174" s="3">
-        <v>31</v>
+        <v>177</v>
       </c>
       <c r="F174" s="3">
-        <v>80.6</v>
+        <v>32.2</v>
       </c>
     </row>
     <row r="175" spans="1:6">
@@ -5686,14 +5686,14 @@
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E175" s="3">
-        <v>167</v>
+        <v>31</v>
       </c>
       <c r="F175" s="3">
-        <v>82.6</v>
+        <v>80.6</v>
       </c>
     </row>
     <row r="176" spans="1:6">
@@ -5712,14 +5712,14 @@
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E176" s="3">
-        <v>68</v>
+        <v>167</v>
       </c>
       <c r="F176" s="3">
-        <v>94.1</v>
+        <v>82.6</v>
       </c>
     </row>
     <row r="177" spans="1:6">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C177" s="3">
@@ -5738,14 +5738,14 @@
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E177" s="3">
-        <v>103</v>
+        <v>68</v>
       </c>
       <c r="F177" s="3">
-        <v>54.4</v>
+        <v>94.1</v>
       </c>
     </row>
     <row r="178" spans="1:6">
@@ -5764,14 +5764,14 @@
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E178" s="3">
-        <v>550</v>
+        <v>103</v>
       </c>
       <c r="F178" s="3">
-        <v>43.6</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="179" spans="1:6">
@@ -5790,14 +5790,14 @@
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E179" s="3">
-        <v>170</v>
+        <v>549</v>
       </c>
       <c r="F179" s="3">
-        <v>32.9</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="180" spans="1:6">
@@ -5808,22 +5808,22 @@
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C180" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E180" s="3">
-        <v>27</v>
+        <v>170</v>
       </c>
       <c r="F180" s="3">
-        <v>81.5</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="181" spans="1:6">
@@ -5842,14 +5842,14 @@
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E181" s="3">
-        <v>147</v>
+        <v>27</v>
       </c>
       <c r="F181" s="3">
-        <v>82.3</v>
+        <v>81.5</v>
       </c>
     </row>
     <row r="182" spans="1:6">
@@ -5868,14 +5868,14 @@
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E182" s="3">
-        <v>62</v>
+        <v>147</v>
       </c>
       <c r="F182" s="3">
-        <v>93.5</v>
+        <v>82.3</v>
       </c>
     </row>
     <row r="183" spans="1:6">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C183" s="3">
@@ -5894,14 +5894,14 @@
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E183" s="3">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="F183" s="3">
-        <v>54.6</v>
+        <v>93.5</v>
       </c>
     </row>
     <row r="184" spans="1:6">
@@ -5920,14 +5920,14 @@
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E184" s="3">
-        <v>533</v>
+        <v>97</v>
       </c>
       <c r="F184" s="3">
-        <v>43.5</v>
+        <v>54.6</v>
       </c>
     </row>
     <row r="185" spans="1:6">
@@ -5946,14 +5946,14 @@
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E185" s="3">
-        <v>160</v>
+        <v>532</v>
       </c>
       <c r="F185" s="3">
-        <v>32.5</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="186" spans="1:6">
@@ -5964,22 +5964,22 @@
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C186" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E186" s="3">
-        <v>23</v>
+        <v>160</v>
       </c>
       <c r="F186" s="3">
-        <v>78.3</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="187" spans="1:6">
@@ -5998,14 +5998,14 @@
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E187" s="3">
-        <v>105</v>
+        <v>23</v>
       </c>
       <c r="F187" s="3">
-        <v>83.8</v>
+        <v>78.3</v>
       </c>
     </row>
     <row r="188" spans="1:6">
@@ -6024,14 +6024,14 @@
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E188" s="3">
-        <v>47</v>
+        <v>105</v>
       </c>
       <c r="F188" s="3">
-        <v>91.5</v>
+        <v>83.8</v>
       </c>
     </row>
     <row r="189" spans="1:6">
@@ -6042,7 +6042,7 @@
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C189" s="3">
@@ -6050,14 +6050,14 @@
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E189" s="3">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="F189" s="3">
-        <v>55.2</v>
+        <v>91.5</v>
       </c>
     </row>
     <row r="190" spans="1:6">
@@ -6076,14 +6076,14 @@
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E190" s="3">
-        <v>462</v>
+        <v>87</v>
       </c>
       <c r="F190" s="3">
-        <v>44.4</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="191" spans="1:6">
@@ -6102,14 +6102,14 @@
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E191" s="3">
-        <v>134</v>
+        <v>461</v>
       </c>
       <c r="F191" s="3">
-        <v>29.1</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="192" spans="1:6">
@@ -6120,22 +6120,22 @@
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C192" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E192" s="3">
-        <v>14</v>
+        <v>134</v>
       </c>
       <c r="F192" s="3">
-        <v>85.7</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="193" spans="1:6">
@@ -6154,14 +6154,14 @@
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E193" s="3">
-        <v>61</v>
+        <v>14</v>
       </c>
       <c r="F193" s="3">
-        <v>90.2</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="194" spans="1:6">
@@ -6180,14 +6180,14 @@
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E194" s="3">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="F194" s="3">
-        <v>97.1</v>
+        <v>90.2</v>
       </c>
     </row>
     <row r="195" spans="1:6">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C195" s="3">
@@ -6206,14 +6206,14 @@
       </c>
       <c r="D195" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E195" s="3">
-        <v>77</v>
+        <v>34</v>
       </c>
       <c r="F195" s="3">
-        <v>55.8</v>
+        <v>97.1</v>
       </c>
     </row>
     <row r="196" spans="1:6">
@@ -6232,14 +6232,14 @@
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E196" s="3">
-        <v>392</v>
+        <v>77</v>
       </c>
       <c r="F196" s="3">
-        <v>46.9</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="197" spans="1:6">
@@ -6258,13 +6258,39 @@
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E197" s="3">
+        <v>391</v>
+      </c>
+      <c r="F197" s="3">
+        <v>46.8</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6">
+      <c r="A198" s="3" t="inlineStr">
+        <is>
+          <t>90日</t>
+        </is>
+      </c>
+      <c r="B198" s="3" t="inlineStr">
+        <is>
+          <t>反T</t>
+        </is>
+      </c>
+      <c r="C198" s="3">
+        <v>20</v>
+      </c>
+      <c r="D198" s="3" t="inlineStr">
+        <is>
           <t>缩量</t>
         </is>
       </c>
-      <c r="E197" s="3">
+      <c r="E198" s="3">
         <v>115</v>
       </c>
-      <c r="F197" s="3">
+      <c r="F198" s="3">
         <v>30.4</v>
       </c>
     </row>
@@ -7610,10 +7636,10 @@
         </is>
       </c>
       <c r="E51" s="3">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="F51" s="3">
-        <v>44.6</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -8208,10 +8234,10 @@
         </is>
       </c>
       <c r="E74" s="3">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="F74" s="3">
-        <v>54.5</v>
+        <v>54.7</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -8338,10 +8364,10 @@
         </is>
       </c>
       <c r="E79" s="3">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F79" s="3">
-        <v>53.7</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -8442,10 +8468,10 @@
         </is>
       </c>
       <c r="E83" s="3">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F83" s="3">
-        <v>52.3</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -8546,10 +8572,10 @@
         </is>
       </c>
       <c r="E87" s="3">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F87" s="3">
-        <v>54.8</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -8936,10 +8962,10 @@
         </is>
       </c>
       <c r="E102" s="3">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="F102" s="3">
-        <v>42.1</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="103" spans="1:6">
@@ -9092,10 +9118,10 @@
         </is>
       </c>
       <c r="E108" s="3">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="F108" s="3">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="109" spans="1:6">
@@ -9248,10 +9274,10 @@
         </is>
       </c>
       <c r="E114" s="3">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="F114" s="3">
-        <v>42.7</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -9404,10 +9430,10 @@
         </is>
       </c>
       <c r="E120" s="3">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="F120" s="3">
-        <v>42.9</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -9560,10 +9586,10 @@
         </is>
       </c>
       <c r="E126" s="3">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="F126" s="3">
-        <v>43.0</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -9716,10 +9742,10 @@
         </is>
       </c>
       <c r="E132" s="3">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="F132" s="3">
-        <v>44.2</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -9779,7 +9805,7 @@
         </is>
       </c>
       <c r="B2" s="3">
-        <v>1500</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -9789,7 +9815,7 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -9953,7 +9979,7 @@
         <v>2.19</v>
       </c>
       <c r="C9" s="3">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -9979,7 +10005,7 @@
         <v>3.21</v>
       </c>
       <c r="C11" s="3">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -10119,7 +10145,7 @@
         <v>0.5</v>
       </c>
       <c r="B2" s="3">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="C2" s="3">
         <v>83.9</v>
@@ -10128,13 +10154,13 @@
         <v>623</v>
       </c>
       <c r="E2" s="3">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="F2" s="3">
-        <v>-0.17</v>
+        <v>-0.16</v>
       </c>
       <c r="G2" s="3">
-        <v>-207.62</v>
+        <v>-206.13</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -10142,7 +10168,7 @@
         <v>1.0</v>
       </c>
       <c r="B3" s="3">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="C3" s="3">
         <v>68.9</v>
@@ -10157,7 +10183,7 @@
         <v>-0.15</v>
       </c>
       <c r="G3" s="3">
-        <v>-154.78</v>
+        <v>-153.79</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -10165,22 +10191,22 @@
         <v>1.5</v>
       </c>
       <c r="B4" s="3">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C4" s="3">
-        <v>55.9</v>
+        <v>55.8</v>
       </c>
       <c r="D4" s="3">
         <v>430</v>
       </c>
       <c r="E4" s="3">
-        <v>51.3</v>
+        <v>51.4</v>
       </c>
       <c r="F4" s="3">
         <v>-0.11</v>
       </c>
       <c r="G4" s="3">
-        <v>-88.84</v>
+        <v>-88.35</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -10188,16 +10214,16 @@
         <v>2.0</v>
       </c>
       <c r="B5" s="3">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C5" s="3">
-        <v>43.9</v>
+        <v>43.8</v>
       </c>
       <c r="D5" s="3">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E5" s="3">
-        <v>51.7</v>
+        <v>51.6</v>
       </c>
       <c r="F5" s="3">
         <v>-0.11</v>
@@ -10211,22 +10237,22 @@
         <v>2.5</v>
       </c>
       <c r="B6" s="3">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C6" s="3">
         <v>35.6</v>
       </c>
       <c r="D6" s="3">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E6" s="3">
-        <v>53.4</v>
+        <v>53.3</v>
       </c>
       <c r="F6" s="3">
         <v>-0.06</v>
       </c>
       <c r="G6" s="3">
-        <v>-30.48</v>
+        <v>-30.97</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -10636,7 +10662,7 @@
         <v>1227</v>
       </c>
       <c r="C2" s="3">
-        <v>81.8</v>
+        <v>81.9</v>
       </c>
       <c r="D2" s="3">
         <v>618</v>
@@ -10659,7 +10685,7 @@
         <v>995</v>
       </c>
       <c r="C3" s="3">
-        <v>66.3</v>
+        <v>66.4</v>
       </c>
       <c r="D3" s="3">
         <v>524</v>
@@ -11219,10 +11245,10 @@
         <v>3</v>
       </c>
       <c r="C5" s="3">
-        <v>54.3</v>
+        <v>54.4</v>
       </c>
       <c r="D5" s="3">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E5" s="3">
         <v>15</v>
@@ -11251,10 +11277,10 @@
         <v>20</v>
       </c>
       <c r="F6" s="3">
-        <v>44.9</v>
+        <v>44.8</v>
       </c>
       <c r="G6" s="3">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
   </sheetData>
@@ -11961,16 +11987,16 @@
         </is>
       </c>
       <c r="C3" s="3">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="D3" s="3">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E3" s="3">
-        <v>45.1</v>
+        <v>45.0</v>
       </c>
       <c r="F3" s="3">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="4" spans="1:6">

--- a/t_analysis/神火股份_000933.SZ抓取数据_T策略分析.xlsx
+++ b/t_analysis/神火股份_000933.SZ抓取数据_T策略分析.xlsx
@@ -558,16 +558,16 @@
         </is>
       </c>
       <c r="C2" s="3">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="D2" s="3">
         <v>251</v>
       </c>
       <c r="E2" s="3">
-        <v>54.4</v>
+        <v>54.2</v>
       </c>
       <c r="F2" s="3">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -602,16 +602,16 @@
         </is>
       </c>
       <c r="C4" s="3">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D4" s="3">
         <v>212</v>
       </c>
       <c r="E4" s="3">
-        <v>53.4</v>
+        <v>53.1</v>
       </c>
       <c r="F4" s="3">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -646,16 +646,16 @@
         </is>
       </c>
       <c r="C6" s="3">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D6" s="3">
         <v>159</v>
       </c>
       <c r="E6" s="3">
-        <v>52.3</v>
+        <v>52.0</v>
       </c>
       <c r="F6" s="3">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -690,16 +690,16 @@
         </is>
       </c>
       <c r="C8" s="3">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D8" s="3">
         <v>137</v>
       </c>
       <c r="E8" s="3">
-        <v>54.4</v>
+        <v>53.9</v>
       </c>
       <c r="F8" s="3">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -892,16 +892,16 @@
         </is>
       </c>
       <c r="C3" s="3">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="D3" s="3">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E3" s="3">
-        <v>42.0</v>
+        <v>42.2</v>
       </c>
       <c r="F3" s="3">
-        <v>6.53</v>
+        <v>6.47</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -936,16 +936,16 @@
         </is>
       </c>
       <c r="C5" s="3">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="D5" s="3">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E5" s="3">
-        <v>42.2</v>
+        <v>42.3</v>
       </c>
       <c r="F5" s="3">
-        <v>6.46</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -980,16 +980,16 @@
         </is>
       </c>
       <c r="C7" s="3">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="D7" s="3">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E7" s="3">
-        <v>42.7</v>
+        <v>42.8</v>
       </c>
       <c r="F7" s="3">
-        <v>6.31</v>
+        <v>6.24</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1024,16 +1024,16 @@
         </is>
       </c>
       <c r="C9" s="3">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="D9" s="3">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="E9" s="3">
-        <v>42.6</v>
+        <v>42.7</v>
       </c>
       <c r="F9" s="3">
-        <v>6.47</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1068,16 +1068,16 @@
         </is>
       </c>
       <c r="C11" s="3">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D11" s="3">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E11" s="3">
-        <v>42.7</v>
+        <v>42.8</v>
       </c>
       <c r="F11" s="3">
-        <v>6.75</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1112,16 +1112,16 @@
         </is>
       </c>
       <c r="C13" s="3">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="D13" s="3">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E13" s="3">
-        <v>44.8</v>
+        <v>45.0</v>
       </c>
       <c r="F13" s="3">
-        <v>6.52</v>
+        <v>6.43</v>
       </c>
     </row>
   </sheetData>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="E2" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" s="3">
-        <v>71.4</v>
+        <v>75.0</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1292,14 +1292,14 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E6" s="3">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="F6" s="3">
-        <v>100.0</v>
+        <v>60.4</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1318,14 +1318,14 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E7" s="3">
-        <v>101</v>
+        <v>333</v>
       </c>
       <c r="F7" s="3">
-        <v>60.4</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1344,14 +1344,14 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E8" s="3">
-        <v>332</v>
+        <v>61</v>
       </c>
       <c r="F8" s="3">
-        <v>48.5</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1362,22 +1362,22 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C9" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E9" s="3">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="F9" s="3">
-        <v>41.0</v>
+        <v>75.0</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1396,14 +1396,14 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E10" s="3">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="F10" s="3">
-        <v>66.7</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1422,14 +1422,14 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E11" s="3">
-        <v>28</v>
+        <v>175</v>
       </c>
       <c r="F11" s="3">
-        <v>46.4</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1448,14 +1448,14 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E12" s="3">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="F12" s="3">
-        <v>43.4</v>
+        <v>60.7</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C13" s="3">
@@ -1474,14 +1474,14 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E13" s="3">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="F13" s="3">
-        <v>60.7</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1500,14 +1500,14 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E14" s="3">
-        <v>83</v>
+        <v>245</v>
       </c>
       <c r="F14" s="3">
-        <v>61.4</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1526,14 +1526,14 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E15" s="3">
-        <v>245</v>
+        <v>34</v>
       </c>
       <c r="F15" s="3">
-        <v>49.0</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1544,22 +1544,22 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C16" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E16" s="3">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F16" s="3">
-        <v>44.1</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1578,14 +1578,14 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E17" s="3">
-        <v>15</v>
+        <v>93</v>
       </c>
       <c r="F17" s="3">
-        <v>53.3</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -1604,14 +1604,14 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E18" s="3">
-        <v>93</v>
+        <v>22</v>
       </c>
       <c r="F18" s="3">
-        <v>39.8</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C19" s="3">
@@ -1630,14 +1630,14 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E19" s="3">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="F19" s="3">
-        <v>40.9</v>
+        <v>67.2</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1656,14 +1656,14 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E20" s="3">
-        <v>61</v>
+        <v>140</v>
       </c>
       <c r="F20" s="3">
-        <v>67.2</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1682,14 +1682,14 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E21" s="3">
-        <v>140</v>
+        <v>14</v>
       </c>
       <c r="F21" s="3">
-        <v>48.6</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -1700,22 +1700,22 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C22" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E22" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F22" s="3">
-        <v>42.9</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -1734,14 +1734,14 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E23" s="3">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="F23" s="3">
-        <v>58.3</v>
+        <v>35.3</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -1760,14 +1760,14 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E24" s="3">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="F24" s="3">
-        <v>35.3</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C25" s="3">
@@ -1786,14 +1786,14 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E25" s="3">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="F25" s="3">
-        <v>35.7</v>
+        <v>68.8</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -1812,14 +1812,14 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E26" s="3">
-        <v>48</v>
+        <v>93</v>
       </c>
       <c r="F26" s="3">
-        <v>68.8</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -1838,14 +1838,14 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E27" s="3">
-        <v>93</v>
+        <v>9</v>
       </c>
       <c r="F27" s="3">
-        <v>52.7</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -1856,22 +1856,22 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C28" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E28" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F28" s="3">
-        <v>44.4</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -1890,14 +1890,14 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E29" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F29" s="3">
-        <v>40.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -1916,14 +1916,14 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E30" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F30" s="3">
-        <v>30.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C31" s="3">
@@ -1942,14 +1942,14 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E31" s="3">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="F31" s="3">
-        <v>0.0</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -1968,14 +1968,14 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E32" s="3">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="F32" s="3">
-        <v>55.6</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -1994,14 +1994,14 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E33" s="3">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="F33" s="3">
-        <v>45.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -2012,15 +2012,15 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C34" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E34" s="3">
@@ -2046,14 +2046,14 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E35" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F35" s="3">
-        <v>0.0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -2072,14 +2072,14 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E36" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F36" s="3">
-        <v>33.3</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C37" s="3">
@@ -2098,14 +2098,14 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E37" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F37" s="3">
-        <v>0.0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -2124,14 +2124,14 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E38" s="3">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F38" s="3">
-        <v>66.7</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -2150,40 +2150,40 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E39" s="3">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F39" s="3">
-        <v>37.5</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>5日</t>
+          <t>10日</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C40" s="3">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E40" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F40" s="3">
-        <v>0.0</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -2202,14 +2202,14 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E41" s="3">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="F41" s="3">
-        <v>11.1</v>
+        <v>73.3</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -2228,14 +2228,14 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E42" s="3">
-        <v>30</v>
+        <v>292</v>
       </c>
       <c r="F42" s="3">
-        <v>73.3</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -2254,14 +2254,14 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E43" s="3">
-        <v>292</v>
+        <v>128</v>
       </c>
       <c r="F43" s="3">
-        <v>54.5</v>
+        <v>57.8</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C44" s="3">
@@ -2280,14 +2280,14 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E44" s="3">
-        <v>128</v>
+        <v>1</v>
       </c>
       <c r="F44" s="3">
-        <v>57.8</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -2306,14 +2306,14 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E45" s="3">
-        <v>3</v>
+        <v>103</v>
       </c>
       <c r="F45" s="3">
-        <v>100.0</v>
+        <v>69.9</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -2332,14 +2332,14 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E46" s="3">
-        <v>103</v>
+        <v>434</v>
       </c>
       <c r="F46" s="3">
-        <v>69.9</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -2358,14 +2358,14 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E47" s="3">
-        <v>432</v>
+        <v>85</v>
       </c>
       <c r="F47" s="3">
-        <v>46.8</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -2376,22 +2376,22 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C48" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E48" s="3">
-        <v>85</v>
+        <v>7</v>
       </c>
       <c r="F48" s="3">
-        <v>40.0</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -2410,14 +2410,14 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E49" s="3">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="F49" s="3">
-        <v>14.3</v>
+        <v>72.7</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -2436,14 +2436,14 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E50" s="3">
-        <v>22</v>
+        <v>226</v>
       </c>
       <c r="F50" s="3">
-        <v>72.7</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -2462,14 +2462,14 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E51" s="3">
-        <v>226</v>
+        <v>95</v>
       </c>
       <c r="F51" s="3">
-        <v>54.4</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C52" s="3">
@@ -2488,14 +2488,14 @@
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E52" s="3">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F52" s="3">
-        <v>51.6</v>
+        <v>68.8</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -2514,14 +2514,14 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E53" s="3">
-        <v>2</v>
+        <v>357</v>
       </c>
       <c r="F53" s="3">
-        <v>100.0</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -2540,14 +2540,14 @@
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E54" s="3">
-        <v>93</v>
+        <v>52</v>
       </c>
       <c r="F54" s="3">
-        <v>68.8</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -2558,22 +2558,22 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C55" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E55" s="3">
-        <v>355</v>
+        <v>1</v>
       </c>
       <c r="F55" s="3">
-        <v>47.9</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -2584,22 +2584,22 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C56" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E56" s="3">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="F56" s="3">
-        <v>42.3</v>
+        <v>70.6</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -2618,14 +2618,14 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E57" s="3">
-        <v>1</v>
+        <v>145</v>
       </c>
       <c r="F57" s="3">
-        <v>0.0</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -2644,14 +2644,14 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E58" s="3">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="F58" s="3">
-        <v>70.6</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C59" s="3">
@@ -2670,14 +2670,14 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E59" s="3">
-        <v>145</v>
+        <v>71</v>
       </c>
       <c r="F59" s="3">
-        <v>52.4</v>
+        <v>70.4</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C60" s="3">
@@ -2696,14 +2696,14 @@
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E60" s="3">
-        <v>53</v>
+        <v>242</v>
       </c>
       <c r="F60" s="3">
-        <v>58.5</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -2722,14 +2722,14 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E61" s="3">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="F61" s="3">
-        <v>100.0</v>
+        <v>42.4</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -2740,11 +2740,11 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C62" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="E62" s="3">
-        <v>71</v>
+        <v>13</v>
       </c>
       <c r="F62" s="3">
-        <v>70.4</v>
+        <v>84.6</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -2766,11 +2766,11 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C63" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
@@ -2778,10 +2778,10 @@
         </is>
       </c>
       <c r="E63" s="3">
-        <v>240</v>
+        <v>111</v>
       </c>
       <c r="F63" s="3">
-        <v>48.8</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -2792,11 +2792,11 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C64" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
@@ -2804,10 +2804,10 @@
         </is>
       </c>
       <c r="E64" s="3">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F64" s="3">
-        <v>42.4</v>
+        <v>64.9</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C65" s="3">
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="E65" s="3">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="F65" s="3">
-        <v>84.6</v>
+        <v>68.3</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C66" s="3">
@@ -2856,10 +2856,10 @@
         </is>
       </c>
       <c r="E66" s="3">
-        <v>111</v>
+        <v>194</v>
       </c>
       <c r="F66" s="3">
-        <v>54.1</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C67" s="3">
@@ -2882,10 +2882,10 @@
         </is>
       </c>
       <c r="E67" s="3">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="F67" s="3">
-        <v>64.9</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -2896,22 +2896,22 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C68" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E68" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F68" s="3">
-        <v>100.0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -2922,22 +2922,22 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C69" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E69" s="3">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="F69" s="3">
-        <v>68.3</v>
+        <v>51.0</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -2948,22 +2948,22 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C70" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E70" s="3">
-        <v>193</v>
+        <v>12</v>
       </c>
       <c r="F70" s="3">
-        <v>47.2</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -2978,18 +2978,18 @@
         </is>
       </c>
       <c r="C71" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E71" s="3">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F71" s="3">
-        <v>39.1</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C72" s="3">
@@ -3008,14 +3008,14 @@
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E72" s="3">
-        <v>6</v>
+        <v>96</v>
       </c>
       <c r="F72" s="3">
-        <v>66.7</v>
+        <v>51.0</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C73" s="3">
@@ -3034,14 +3034,14 @@
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E73" s="3">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="F73" s="3">
-        <v>51.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -3056,18 +3056,18 @@
         </is>
       </c>
       <c r="C74" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E74" s="3">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F74" s="3">
-        <v>50.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -3078,22 +3078,22 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C75" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E75" s="3">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F75" s="3">
-        <v>63.6</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -3104,22 +3104,22 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C76" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E76" s="3">
-        <v>96</v>
+        <v>3</v>
       </c>
       <c r="F76" s="3">
-        <v>51.0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -3134,18 +3134,18 @@
         </is>
       </c>
       <c r="C77" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E77" s="3">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F77" s="3">
-        <v>50.0</v>
+        <v>68.4</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C78" s="3">
@@ -3164,14 +3164,14 @@
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E78" s="3">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="F78" s="3">
-        <v>0.0</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -3182,7 +3182,7 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C79" s="3">
@@ -3190,20 +3190,20 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E79" s="3">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F79" s="3">
-        <v>57.1</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>10日</t>
+          <t>20日</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -3212,76 +3212,76 @@
         </is>
       </c>
       <c r="C80" s="3">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E80" s="3">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="F80" s="3">
-        <v>66.7</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>10日</t>
+          <t>20日</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C81" s="3">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E81" s="3">
-        <v>19</v>
+        <v>313</v>
       </c>
       <c r="F81" s="3">
-        <v>68.4</v>
+        <v>54.6</v>
       </c>
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>10日</t>
+          <t>20日</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C82" s="3">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E82" s="3">
-        <v>40</v>
+        <v>111</v>
       </c>
       <c r="F82" s="3">
-        <v>57.5</v>
+        <v>63.1</v>
       </c>
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>10日</t>
+          <t>20日</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -3290,18 +3290,18 @@
         </is>
       </c>
       <c r="C83" s="3">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E83" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F83" s="3">
-        <v>25.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -3312,7 +3312,7 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C84" s="3">
@@ -3324,10 +3324,10 @@
         </is>
       </c>
       <c r="E84" s="3">
-        <v>42</v>
+        <v>102</v>
       </c>
       <c r="F84" s="3">
-        <v>61.9</v>
+        <v>55.9</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C85" s="3">
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="E85" s="3">
-        <v>313</v>
+        <v>466</v>
       </c>
       <c r="F85" s="3">
-        <v>54.6</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C86" s="3">
@@ -3376,10 +3376,10 @@
         </is>
       </c>
       <c r="E86" s="3">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="F86" s="3">
-        <v>63.1</v>
+        <v>28.7</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -3390,22 +3390,22 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C87" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E87" s="3">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="F87" s="3">
-        <v>100.0</v>
+        <v>70.6</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C88" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E88" s="3">
-        <v>102</v>
+        <v>256</v>
       </c>
       <c r="F88" s="3">
-        <v>55.9</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -3442,22 +3442,22 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C89" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E89" s="3">
-        <v>464</v>
+        <v>90</v>
       </c>
       <c r="F89" s="3">
-        <v>46.1</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -3472,18 +3472,18 @@
         </is>
       </c>
       <c r="C90" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E90" s="3">
-        <v>129</v>
+        <v>6</v>
       </c>
       <c r="F90" s="3">
-        <v>28.7</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C91" s="3">
@@ -3506,10 +3506,10 @@
         </is>
       </c>
       <c r="E91" s="3">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="F91" s="3">
-        <v>70.6</v>
+        <v>56.8</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C92" s="3">
@@ -3532,10 +3532,10 @@
         </is>
       </c>
       <c r="E92" s="3">
-        <v>256</v>
+        <v>418</v>
       </c>
       <c r="F92" s="3">
-        <v>55.5</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C93" s="3">
@@ -3558,10 +3558,10 @@
         </is>
       </c>
       <c r="E93" s="3">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F93" s="3">
-        <v>61.1</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="94" spans="1:6">
@@ -3572,22 +3572,22 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C94" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E94" s="3">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="F94" s="3">
-        <v>100.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -3598,22 +3598,22 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C95" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E95" s="3">
-        <v>95</v>
+        <v>188</v>
       </c>
       <c r="F95" s="3">
-        <v>56.8</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="96" spans="1:6">
@@ -3624,22 +3624,22 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C96" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E96" s="3">
-        <v>416</v>
+        <v>67</v>
       </c>
       <c r="F96" s="3">
-        <v>46.4</v>
+        <v>64.2</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -3654,18 +3654,18 @@
         </is>
       </c>
       <c r="C97" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E97" s="3">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="F97" s="3">
-        <v>33.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="98" spans="1:6">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C98" s="3">
@@ -3688,10 +3688,10 @@
         </is>
       </c>
       <c r="E98" s="3">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="F98" s="3">
-        <v>68.0</v>
+        <v>59.0</v>
       </c>
     </row>
     <row r="99" spans="1:6">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C99" s="3">
@@ -3714,10 +3714,10 @@
         </is>
       </c>
       <c r="E99" s="3">
-        <v>188</v>
+        <v>351</v>
       </c>
       <c r="F99" s="3">
-        <v>53.7</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="100" spans="1:6">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C100" s="3">
@@ -3740,10 +3740,10 @@
         </is>
       </c>
       <c r="E100" s="3">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F100" s="3">
-        <v>64.2</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="101" spans="1:6">
@@ -3754,22 +3754,22 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C101" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E101" s="3">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F101" s="3">
-        <v>100.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="102" spans="1:6">
@@ -3780,22 +3780,22 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C102" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E102" s="3">
-        <v>78</v>
+        <v>145</v>
       </c>
       <c r="F102" s="3">
-        <v>59.0</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="103" spans="1:6">
@@ -3806,22 +3806,22 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C103" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E103" s="3">
-        <v>349</v>
+        <v>46</v>
       </c>
       <c r="F103" s="3">
-        <v>45.8</v>
+        <v>73.9</v>
       </c>
     </row>
     <row r="104" spans="1:6">
@@ -3836,18 +3836,18 @@
         </is>
       </c>
       <c r="C104" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E104" s="3">
-        <v>66</v>
+        <v>4</v>
       </c>
       <c r="F104" s="3">
-        <v>36.4</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="105" spans="1:6">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C105" s="3">
@@ -3870,10 +3870,10 @@
         </is>
       </c>
       <c r="E105" s="3">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="F105" s="3">
-        <v>65.0</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="106" spans="1:6">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C106" s="3">
@@ -3896,10 +3896,10 @@
         </is>
       </c>
       <c r="E106" s="3">
-        <v>145</v>
+        <v>303</v>
       </c>
       <c r="F106" s="3">
-        <v>57.2</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="107" spans="1:6">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C107" s="3">
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="E107" s="3">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="F107" s="3">
-        <v>73.9</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="108" spans="1:6">
@@ -3936,22 +3936,22 @@
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C108" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E108" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F108" s="3">
-        <v>100.0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="109" spans="1:6">
@@ -3962,22 +3962,22 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C109" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E109" s="3">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="F109" s="3">
-        <v>59.7</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="110" spans="1:6">
@@ -3988,22 +3988,22 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C110" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E110" s="3">
-        <v>303</v>
+        <v>30</v>
       </c>
       <c r="F110" s="3">
-        <v>47.2</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="111" spans="1:6">
@@ -4018,18 +4018,18 @@
         </is>
       </c>
       <c r="C111" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E111" s="3">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F111" s="3">
-        <v>34.0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="112" spans="1:6">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C112" s="3">
@@ -4048,14 +4048,14 @@
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E112" s="3">
-        <v>9</v>
+        <v>207</v>
       </c>
       <c r="F112" s="3">
-        <v>66.7</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C113" s="3">
@@ -4074,14 +4074,14 @@
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E113" s="3">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="F113" s="3">
-        <v>52.0</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -4096,18 +4096,18 @@
         </is>
       </c>
       <c r="C114" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E114" s="3">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="F114" s="3">
-        <v>83.3</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -4118,22 +4118,22 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C115" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E115" s="3">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F115" s="3">
-        <v>66.7</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="116" spans="1:6">
@@ -4144,22 +4144,22 @@
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C116" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E116" s="3">
-        <v>207</v>
+        <v>12</v>
       </c>
       <c r="F116" s="3">
-        <v>44.4</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -4174,18 +4174,18 @@
         </is>
       </c>
       <c r="C117" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E117" s="3">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F117" s="3">
-        <v>29.6</v>
+        <v>75.9</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C118" s="3">
@@ -4204,14 +4204,14 @@
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E118" s="3">
-        <v>3</v>
+        <v>134</v>
       </c>
       <c r="F118" s="3">
-        <v>100.0</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="119" spans="1:6">
@@ -4222,7 +4222,7 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C119" s="3">
@@ -4230,20 +4230,20 @@
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E119" s="3">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="F119" s="3">
-        <v>38.5</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>20日</t>
+          <t>30日</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -4252,33 +4252,33 @@
         </is>
       </c>
       <c r="C120" s="3">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E120" s="3">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F120" s="3">
-        <v>83.3</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>20日</t>
+          <t>30日</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C121" s="3">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
@@ -4286,25 +4286,25 @@
         </is>
       </c>
       <c r="E121" s="3">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F121" s="3">
-        <v>75.9</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>20日</t>
+          <t>30日</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C122" s="3">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
@@ -4312,25 +4312,25 @@
         </is>
       </c>
       <c r="E122" s="3">
-        <v>134</v>
+        <v>315</v>
       </c>
       <c r="F122" s="3">
-        <v>45.5</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>20日</t>
+          <t>30日</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C123" s="3">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
@@ -4338,10 +4338,10 @@
         </is>
       </c>
       <c r="E123" s="3">
-        <v>15</v>
+        <v>105</v>
       </c>
       <c r="F123" s="3">
-        <v>33.3</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -4352,7 +4352,7 @@
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C124" s="3">
@@ -4360,14 +4360,14 @@
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E124" s="3">
-        <v>5</v>
+        <v>112</v>
       </c>
       <c r="F124" s="3">
-        <v>0.0</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="125" spans="1:6">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C125" s="3">
@@ -4386,14 +4386,14 @@
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E125" s="3">
-        <v>38</v>
+        <v>523</v>
       </c>
       <c r="F125" s="3">
-        <v>52.6</v>
+        <v>44.0</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C126" s="3">
@@ -4412,14 +4412,14 @@
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E126" s="3">
-        <v>313</v>
+        <v>145</v>
       </c>
       <c r="F126" s="3">
-        <v>51.8</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -4434,18 +4434,18 @@
         </is>
       </c>
       <c r="C127" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E127" s="3">
-        <v>105</v>
+        <v>4</v>
       </c>
       <c r="F127" s="3">
-        <v>65.7</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -4456,11 +4456,11 @@
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C128" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
@@ -4468,10 +4468,10 @@
         </is>
       </c>
       <c r="E128" s="3">
-        <v>112</v>
+        <v>27</v>
       </c>
       <c r="F128" s="3">
-        <v>57.1</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -4482,11 +4482,11 @@
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C129" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
@@ -4494,10 +4494,10 @@
         </is>
       </c>
       <c r="E129" s="3">
-        <v>523</v>
+        <v>270</v>
       </c>
       <c r="F129" s="3">
-        <v>44.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -4508,11 +4508,11 @@
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C130" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
@@ -4520,10 +4520,10 @@
         </is>
       </c>
       <c r="E130" s="3">
-        <v>145</v>
+        <v>98</v>
       </c>
       <c r="F130" s="3">
-        <v>24.1</v>
+        <v>67.3</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C131" s="3">
@@ -4542,14 +4542,14 @@
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E131" s="3">
-        <v>2</v>
+        <v>106</v>
       </c>
       <c r="F131" s="3">
-        <v>0.0</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C132" s="3">
@@ -4568,14 +4568,14 @@
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E132" s="3">
-        <v>27</v>
+        <v>479</v>
       </c>
       <c r="F132" s="3">
-        <v>40.7</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C133" s="3">
@@ -4594,14 +4594,14 @@
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E133" s="3">
-        <v>270</v>
+        <v>121</v>
       </c>
       <c r="F133" s="3">
-        <v>50.0</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="134" spans="1:6">
@@ -4616,18 +4616,18 @@
         </is>
       </c>
       <c r="C134" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E134" s="3">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="F134" s="3">
-        <v>67.3</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="135" spans="1:6">
@@ -4638,11 +4638,11 @@
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C135" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
@@ -4650,10 +4650,10 @@
         </is>
       </c>
       <c r="E135" s="3">
-        <v>106</v>
+        <v>23</v>
       </c>
       <c r="F135" s="3">
-        <v>58.5</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -4664,11 +4664,11 @@
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C136" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
@@ -4676,10 +4676,10 @@
         </is>
       </c>
       <c r="E136" s="3">
-        <v>479</v>
+        <v>205</v>
       </c>
       <c r="F136" s="3">
-        <v>44.1</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -4690,11 +4690,11 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C137" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
@@ -4702,10 +4702,10 @@
         </is>
       </c>
       <c r="E137" s="3">
-        <v>121</v>
+        <v>74</v>
       </c>
       <c r="F137" s="3">
-        <v>22.3</v>
+        <v>67.6</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C138" s="3">
@@ -4724,14 +4724,14 @@
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>放量</t>
         </is>
       </c>
       <c r="E138" s="3">
-        <v>2</v>
+        <v>98</v>
       </c>
       <c r="F138" s="3">
-        <v>0.0</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C139" s="3">
@@ -4750,14 +4750,14 @@
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>放量</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="E139" s="3">
-        <v>23</v>
+        <v>405</v>
       </c>
       <c r="F139" s="3">
-        <v>43.5</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C140" s="3">
@@ -4776,14 +4776,14 @@
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>缩量</t>
         </is>
       </c>
       <c r="E140" s="3">
-        <v>205</v>
+        <v>97</v>
       </c>
       <c r="F140" s="3">
-        <v>48.3</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -4798,18 +4798,18 @@
         </is>
       </c>
       <c r="C141" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>缩量</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E141" s="3">
-        <v>74</v>
+        <v>2</v>
       </c>
       <c r="F141" s="3">
-        <v>67.6</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -4820,11 +4820,11 @@
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C142" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
@@ -4832,10 +4832,10 @@
         </is>
       </c>
       <c r="E142" s="3">
-        <v>98</v>
+        <v>21</v>
       </c>
       <c r="F142" s="3">
-        <v>58.2</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -4846,11 +4846,11 @@
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C143" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
@@ -4858,10 +4858,10 @@
         </is>
       </c>
       <c r="E143" s="3">
-        <v>405</v>
+        <v>165</v>
       </c>
       <c r="F143" s="3">
-        <v>45.7</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -4872,11 +4872,11 @@
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C144" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
@@ -4884,10 +4884,10 @@
         </is>
       </c>
       <c r="E144" s="3">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="F144" s="3">
-        <v>20.6</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C145" s="3">
@@ -4910,10 +4910,10 @@
         </is>
       </c>
       <c r="E145" s="3">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="F145" s="3">
-        <v>38.1</v>
+        <v>62.2</v>
       </c>
     </row>
     <row r="146" spans="1:6">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C146" s="3">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="E146" s="3">
-        <v>165</v>
+        <v>351</v>
       </c>
       <c r="F146" s="3">
-        <v>50.3</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C147" s="3">
@@ -4962,10 +4962,10 @@
         </is>
       </c>
       <c r="E147" s="3">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="F147" s="3">
-        <v>69.7</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="148" spans="1:6">
@@ -4976,11 +4976,11 @@
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C148" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="E148" s="3">
-        <v>90</v>
+        <v>14</v>
       </c>
       <c r="F148" s="3">
-        <v>62.2</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="149" spans="1:6">
@@ -5002,11 +5002,11 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C149" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
@@ -5014,10 +5014,10 @@
         </is>
       </c>
       <c r="E149" s="3">
-        <v>351</v>
+        <v>98</v>
       </c>
       <c r="F149" s="3">
-        <v>45.9</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="150" spans="1:6">
@@ -5028,11 +5028,11 @@
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C150" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
@@ -5040,10 +5040,10 @@
         </is>
       </c>
       <c r="E150" s="3">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="F150" s="3">
-        <v>21.9</v>
+        <v>73.2</v>
       </c>
     </row>
     <row r="151" spans="1:6">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C151" s="3">
@@ -5066,10 +5066,10 @@
         </is>
       </c>
       <c r="E151" s="3">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="F151" s="3">
-        <v>42.9</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="152" spans="1:6">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C152" s="3">
@@ -5092,10 +5092,10 @@
         </is>
       </c>
       <c r="E152" s="3">
-        <v>98</v>
+        <v>259</v>
       </c>
       <c r="F152" s="3">
-        <v>46.9</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="153" spans="1:6">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C153" s="3">
@@ -5118,10 +5118,10 @@
         </is>
       </c>
       <c r="E153" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F153" s="3">
-        <v>73.2</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -5132,11 +5132,11 @@
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C154" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
@@ -5144,10 +5144,10 @@
         </is>
       </c>
       <c r="E154" s="3">
-        <v>67</v>
+        <v>6</v>
       </c>
       <c r="F154" s="3">
-        <v>65.7</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="155" spans="1:6">
@@ -5158,11 +5158,11 @@
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C155" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
@@ -5170,10 +5170,10 @@
         </is>
       </c>
       <c r="E155" s="3">
-        <v>259</v>
+        <v>56</v>
       </c>
       <c r="F155" s="3">
-        <v>49.0</v>
+        <v>41.1</v>
       </c>
     </row>
     <row r="156" spans="1:6">
@@ -5184,11 +5184,11 @@
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C156" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
@@ -5196,10 +5196,10 @@
         </is>
       </c>
       <c r="E156" s="3">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="F156" s="3">
-        <v>21.4</v>
+        <v>78.3</v>
       </c>
     </row>
     <row r="157" spans="1:6">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C157" s="3">
@@ -5222,10 +5222,10 @@
         </is>
       </c>
       <c r="E157" s="3">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="F157" s="3">
-        <v>50.0</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="158" spans="1:6">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C158" s="3">
@@ -5248,10 +5248,10 @@
         </is>
       </c>
       <c r="E158" s="3">
-        <v>56</v>
+        <v>194</v>
       </c>
       <c r="F158" s="3">
-        <v>41.1</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="159" spans="1:6">
@@ -5262,7 +5262,7 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C159" s="3">
@@ -5274,25 +5274,25 @@
         </is>
       </c>
       <c r="E159" s="3">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F159" s="3">
-        <v>78.3</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>30日</t>
+          <t>90日</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C160" s="3">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
@@ -5300,25 +5300,25 @@
         </is>
       </c>
       <c r="E160" s="3">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="F160" s="3">
-        <v>62.7</v>
+        <v>77.5</v>
       </c>
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>30日</t>
+          <t>90日</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C161" s="3">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
@@ -5326,25 +5326,25 @@
         </is>
       </c>
       <c r="E161" s="3">
-        <v>194</v>
+        <v>226</v>
       </c>
       <c r="F161" s="3">
-        <v>47.4</v>
+        <v>77.4</v>
       </c>
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>30日</t>
+          <t>90日</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C162" s="3">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
@@ -5352,10 +5352,10 @@
         </is>
       </c>
       <c r="E162" s="3">
-        <v>26</v>
+        <v>84</v>
       </c>
       <c r="F162" s="3">
-        <v>15.4</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="163" spans="1:6">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C163" s="3">
@@ -5378,10 +5378,10 @@
         </is>
       </c>
       <c r="E163" s="3">
-        <v>40</v>
+        <v>116</v>
       </c>
       <c r="F163" s="3">
-        <v>77.5</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="164" spans="1:6">
@@ -5392,7 +5392,7 @@
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C164" s="3">
@@ -5404,10 +5404,10 @@
         </is>
       </c>
       <c r="E164" s="3">
-        <v>226</v>
+        <v>599</v>
       </c>
       <c r="F164" s="3">
-        <v>77.4</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="165" spans="1:6">
@@ -5418,7 +5418,7 @@
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C165" s="3">
@@ -5430,10 +5430,10 @@
         </is>
       </c>
       <c r="E165" s="3">
-        <v>84</v>
+        <v>184</v>
       </c>
       <c r="F165" s="3">
-        <v>95.2</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="166" spans="1:6">
@@ -5444,11 +5444,11 @@
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C166" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
@@ -5456,10 +5456,10 @@
         </is>
       </c>
       <c r="E166" s="3">
-        <v>116</v>
+        <v>38</v>
       </c>
       <c r="F166" s="3">
-        <v>50.9</v>
+        <v>78.9</v>
       </c>
     </row>
     <row r="167" spans="1:6">
@@ -5470,11 +5470,11 @@
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C167" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
@@ -5482,10 +5482,10 @@
         </is>
       </c>
       <c r="E167" s="3">
-        <v>597</v>
+        <v>196</v>
       </c>
       <c r="F167" s="3">
-        <v>43.2</v>
+        <v>79.6</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -5496,11 +5496,11 @@
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C168" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
@@ -5508,10 +5508,10 @@
         </is>
       </c>
       <c r="E168" s="3">
-        <v>184</v>
+        <v>76</v>
       </c>
       <c r="F168" s="3">
-        <v>32.6</v>
+        <v>94.7</v>
       </c>
     </row>
     <row r="169" spans="1:6">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C169" s="3">
@@ -5534,10 +5534,10 @@
         </is>
       </c>
       <c r="E169" s="3">
-        <v>38</v>
+        <v>113</v>
       </c>
       <c r="F169" s="3">
-        <v>78.9</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="170" spans="1:6">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C170" s="3">
@@ -5560,10 +5560,10 @@
         </is>
       </c>
       <c r="E170" s="3">
-        <v>196</v>
+        <v>580</v>
       </c>
       <c r="F170" s="3">
-        <v>79.6</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="171" spans="1:6">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C171" s="3">
@@ -5586,10 +5586,10 @@
         </is>
       </c>
       <c r="E171" s="3">
-        <v>76</v>
+        <v>177</v>
       </c>
       <c r="F171" s="3">
-        <v>94.7</v>
+        <v>32.2</v>
       </c>
     </row>
     <row r="172" spans="1:6">
@@ -5600,11 +5600,11 @@
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C172" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
@@ -5612,10 +5612,10 @@
         </is>
       </c>
       <c r="E172" s="3">
-        <v>113</v>
+        <v>31</v>
       </c>
       <c r="F172" s="3">
-        <v>52.2</v>
+        <v>80.6</v>
       </c>
     </row>
     <row r="173" spans="1:6">
@@ -5626,11 +5626,11 @@
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C173" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="E173" s="3">
-        <v>578</v>
+        <v>167</v>
       </c>
       <c r="F173" s="3">
-        <v>43.3</v>
+        <v>82.6</v>
       </c>
     </row>
     <row r="174" spans="1:6">
@@ -5652,11 +5652,11 @@
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C174" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
@@ -5664,10 +5664,10 @@
         </is>
       </c>
       <c r="E174" s="3">
-        <v>177</v>
+        <v>68</v>
       </c>
       <c r="F174" s="3">
-        <v>32.2</v>
+        <v>94.1</v>
       </c>
     </row>
     <row r="175" spans="1:6">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C175" s="3">
@@ -5690,10 +5690,10 @@
         </is>
       </c>
       <c r="E175" s="3">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="F175" s="3">
-        <v>80.6</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="176" spans="1:6">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C176" s="3">
@@ -5716,10 +5716,10 @@
         </is>
       </c>
       <c r="E176" s="3">
-        <v>167</v>
+        <v>551</v>
       </c>
       <c r="F176" s="3">
-        <v>82.6</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="177" spans="1:6">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C177" s="3">
@@ -5742,10 +5742,10 @@
         </is>
       </c>
       <c r="E177" s="3">
-        <v>68</v>
+        <v>170</v>
       </c>
       <c r="F177" s="3">
-        <v>94.1</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="178" spans="1:6">
@@ -5756,11 +5756,11 @@
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C178" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
@@ -5768,10 +5768,10 @@
         </is>
       </c>
       <c r="E178" s="3">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="F178" s="3">
-        <v>54.4</v>
+        <v>81.5</v>
       </c>
     </row>
     <row r="179" spans="1:6">
@@ -5782,11 +5782,11 @@
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C179" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
@@ -5794,10 +5794,10 @@
         </is>
       </c>
       <c r="E179" s="3">
-        <v>549</v>
+        <v>147</v>
       </c>
       <c r="F179" s="3">
-        <v>43.5</v>
+        <v>82.3</v>
       </c>
     </row>
     <row r="180" spans="1:6">
@@ -5808,11 +5808,11 @@
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C180" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
@@ -5820,10 +5820,10 @@
         </is>
       </c>
       <c r="E180" s="3">
-        <v>170</v>
+        <v>62</v>
       </c>
       <c r="F180" s="3">
-        <v>32.9</v>
+        <v>93.5</v>
       </c>
     </row>
     <row r="181" spans="1:6">
@@ -5834,7 +5834,7 @@
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C181" s="3">
@@ -5846,10 +5846,10 @@
         </is>
       </c>
       <c r="E181" s="3">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="F181" s="3">
-        <v>81.5</v>
+        <v>54.6</v>
       </c>
     </row>
     <row r="182" spans="1:6">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C182" s="3">
@@ -5872,10 +5872,10 @@
         </is>
       </c>
       <c r="E182" s="3">
-        <v>147</v>
+        <v>534</v>
       </c>
       <c r="F182" s="3">
-        <v>82.3</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="183" spans="1:6">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C183" s="3">
@@ -5898,10 +5898,10 @@
         </is>
       </c>
       <c r="E183" s="3">
-        <v>62</v>
+        <v>160</v>
       </c>
       <c r="F183" s="3">
-        <v>93.5</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="184" spans="1:6">
@@ -5912,11 +5912,11 @@
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C184" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
@@ -5924,10 +5924,10 @@
         </is>
       </c>
       <c r="E184" s="3">
-        <v>97</v>
+        <v>23</v>
       </c>
       <c r="F184" s="3">
-        <v>54.6</v>
+        <v>78.3</v>
       </c>
     </row>
     <row r="185" spans="1:6">
@@ -5938,11 +5938,11 @@
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C185" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
@@ -5950,10 +5950,10 @@
         </is>
       </c>
       <c r="E185" s="3">
-        <v>532</v>
+        <v>105</v>
       </c>
       <c r="F185" s="3">
-        <v>43.4</v>
+        <v>83.8</v>
       </c>
     </row>
     <row r="186" spans="1:6">
@@ -5964,11 +5964,11 @@
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C186" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
@@ -5976,10 +5976,10 @@
         </is>
       </c>
       <c r="E186" s="3">
-        <v>160</v>
+        <v>47</v>
       </c>
       <c r="F186" s="3">
-        <v>32.5</v>
+        <v>91.5</v>
       </c>
     </row>
     <row r="187" spans="1:6">
@@ -5990,7 +5990,7 @@
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C187" s="3">
@@ -6002,10 +6002,10 @@
         </is>
       </c>
       <c r="E187" s="3">
-        <v>23</v>
+        <v>87</v>
       </c>
       <c r="F187" s="3">
-        <v>78.3</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="188" spans="1:6">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C188" s="3">
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="E188" s="3">
-        <v>105</v>
+        <v>463</v>
       </c>
       <c r="F188" s="3">
-        <v>83.8</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="189" spans="1:6">
@@ -6042,7 +6042,7 @@
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C189" s="3">
@@ -6054,10 +6054,10 @@
         </is>
       </c>
       <c r="E189" s="3">
-        <v>47</v>
+        <v>134</v>
       </c>
       <c r="F189" s="3">
-        <v>91.5</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="190" spans="1:6">
@@ -6068,11 +6068,11 @@
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C190" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
@@ -6080,10 +6080,10 @@
         </is>
       </c>
       <c r="E190" s="3">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="F190" s="3">
-        <v>55.2</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="191" spans="1:6">
@@ -6094,11 +6094,11 @@
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C191" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
@@ -6106,10 +6106,10 @@
         </is>
       </c>
       <c r="E191" s="3">
-        <v>461</v>
+        <v>61</v>
       </c>
       <c r="F191" s="3">
-        <v>44.3</v>
+        <v>90.2</v>
       </c>
     </row>
     <row r="192" spans="1:6">
@@ -6120,11 +6120,11 @@
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>反T</t>
+          <t>正T</t>
         </is>
       </c>
       <c r="C192" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
@@ -6132,10 +6132,10 @@
         </is>
       </c>
       <c r="E192" s="3">
-        <v>134</v>
+        <v>34</v>
       </c>
       <c r="F192" s="3">
-        <v>29.1</v>
+        <v>97.1</v>
       </c>
     </row>
     <row r="193" spans="1:6">
@@ -6146,7 +6146,7 @@
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C193" s="3">
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="E193" s="3">
-        <v>14</v>
+        <v>77</v>
       </c>
       <c r="F193" s="3">
-        <v>85.7</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="194" spans="1:6">
@@ -6172,7 +6172,7 @@
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C194" s="3">
@@ -6184,10 +6184,10 @@
         </is>
       </c>
       <c r="E194" s="3">
-        <v>61</v>
+        <v>393</v>
       </c>
       <c r="F194" s="3">
-        <v>90.2</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="195" spans="1:6">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>正T</t>
+          <t>反T</t>
         </is>
       </c>
       <c r="C195" s="3">
@@ -6210,87 +6210,9 @@
         </is>
       </c>
       <c r="E195" s="3">
-        <v>34</v>
+        <v>115</v>
       </c>
       <c r="F195" s="3">
-        <v>97.1</v>
-      </c>
-    </row>
-    <row r="196" spans="1:6">
-      <c r="A196" s="3" t="inlineStr">
-        <is>
-          <t>90日</t>
-        </is>
-      </c>
-      <c r="B196" s="3" t="inlineStr">
-        <is>
-          <t>反T</t>
-        </is>
-      </c>
-      <c r="C196" s="3">
-        <v>20</v>
-      </c>
-      <c r="D196" s="3" t="inlineStr">
-        <is>
-          <t>放量</t>
-        </is>
-      </c>
-      <c r="E196" s="3">
-        <v>77</v>
-      </c>
-      <c r="F196" s="3">
-        <v>55.8</v>
-      </c>
-    </row>
-    <row r="197" spans="1:6">
-      <c r="A197" s="3" t="inlineStr">
-        <is>
-          <t>90日</t>
-        </is>
-      </c>
-      <c r="B197" s="3" t="inlineStr">
-        <is>
-          <t>反T</t>
-        </is>
-      </c>
-      <c r="C197" s="3">
-        <v>20</v>
-      </c>
-      <c r="D197" s="3" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="E197" s="3">
-        <v>391</v>
-      </c>
-      <c r="F197" s="3">
-        <v>46.8</v>
-      </c>
-    </row>
-    <row r="198" spans="1:6">
-      <c r="A198" s="3" t="inlineStr">
-        <is>
-          <t>90日</t>
-        </is>
-      </c>
-      <c r="B198" s="3" t="inlineStr">
-        <is>
-          <t>反T</t>
-        </is>
-      </c>
-      <c r="C198" s="3">
-        <v>20</v>
-      </c>
-      <c r="D198" s="3" t="inlineStr">
-        <is>
-          <t>缩量</t>
-        </is>
-      </c>
-      <c r="E198" s="3">
-        <v>115</v>
-      </c>
-      <c r="F198" s="3">
         <v>30.4</v>
       </c>
     </row>
@@ -6388,10 +6310,10 @@
         </is>
       </c>
       <c r="E3" s="3">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F3" s="3">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -6492,10 +6414,10 @@
         </is>
       </c>
       <c r="E7" s="3">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F7" s="3">
-        <v>46.9</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -7636,10 +7558,10 @@
         </is>
       </c>
       <c r="E51" s="3">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="F51" s="3">
-        <v>44.5</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -8234,10 +8156,10 @@
         </is>
       </c>
       <c r="E74" s="3">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F74" s="3">
-        <v>54.7</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -8364,10 +8286,10 @@
         </is>
       </c>
       <c r="E79" s="3">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="F79" s="3">
-        <v>53.8</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -8468,10 +8390,10 @@
         </is>
       </c>
       <c r="E83" s="3">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F83" s="3">
-        <v>52.5</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -8572,10 +8494,10 @@
         </is>
       </c>
       <c r="E87" s="3">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F87" s="3">
-        <v>55.0</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -8962,10 +8884,10 @@
         </is>
       </c>
       <c r="E102" s="3">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="F102" s="3">
-        <v>42.0</v>
+        <v>42.2</v>
       </c>
     </row>
     <row r="103" spans="1:6">
@@ -9118,10 +9040,10 @@
         </is>
       </c>
       <c r="E108" s="3">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="F108" s="3">
-        <v>42.1</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="109" spans="1:6">
@@ -9274,10 +9196,10 @@
         </is>
       </c>
       <c r="E114" s="3">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="F114" s="3">
-        <v>42.6</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -9430,10 +9352,10 @@
         </is>
       </c>
       <c r="E120" s="3">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="F120" s="3">
-        <v>42.8</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -9586,10 +9508,10 @@
         </is>
       </c>
       <c r="E126" s="3">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="F126" s="3">
-        <v>42.9</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -9742,10 +9664,10 @@
         </is>
       </c>
       <c r="E132" s="3">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="F132" s="3">
-        <v>44.1</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -9805,7 +9727,7 @@
         </is>
       </c>
       <c r="B2" s="3">
-        <v>1499</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -9815,7 +9737,7 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -9825,7 +9747,7 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -9979,7 +9901,7 @@
         <v>2.19</v>
       </c>
       <c r="C9" s="3">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -9989,7 +9911,7 @@
         </is>
       </c>
       <c r="B10" s="3">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="C10" s="3">
         <v>2.4</v>
@@ -10005,7 +9927,7 @@
         <v>3.21</v>
       </c>
       <c r="C11" s="3">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -10145,13 +10067,13 @@
         <v>0.5</v>
       </c>
       <c r="B2" s="3">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="C2" s="3">
         <v>83.9</v>
       </c>
       <c r="D2" s="3">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="E2" s="3">
         <v>49.6</v>
@@ -10160,7 +10082,7 @@
         <v>-0.16</v>
       </c>
       <c r="G2" s="3">
-        <v>-206.13</v>
+        <v>-206.4</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -10168,13 +10090,13 @@
         <v>1.0</v>
       </c>
       <c r="B3" s="3">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="C3" s="3">
-        <v>68.9</v>
+        <v>69.0</v>
       </c>
       <c r="D3" s="3">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E3" s="3">
         <v>51.0</v>
@@ -10183,7 +10105,7 @@
         <v>-0.15</v>
       </c>
       <c r="G3" s="3">
-        <v>-153.79</v>
+        <v>-153.08</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -10191,22 +10113,22 @@
         <v>1.5</v>
       </c>
       <c r="B4" s="3">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="C4" s="3">
-        <v>55.8</v>
+        <v>55.9</v>
       </c>
       <c r="D4" s="3">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E4" s="3">
         <v>51.4</v>
       </c>
       <c r="F4" s="3">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="G4" s="3">
-        <v>-88.35</v>
+        <v>-86.65</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -10214,22 +10136,22 @@
         <v>2.0</v>
       </c>
       <c r="B5" s="3">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="C5" s="3">
-        <v>43.8</v>
+        <v>43.9</v>
       </c>
       <c r="D5" s="3">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E5" s="3">
-        <v>51.6</v>
+        <v>51.7</v>
       </c>
       <c r="F5" s="3">
         <v>-0.11</v>
       </c>
       <c r="G5" s="3">
-        <v>-73.87</v>
+        <v>-71.2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -10237,22 +10159,22 @@
         <v>2.5</v>
       </c>
       <c r="B6" s="3">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C6" s="3">
         <v>35.6</v>
       </c>
       <c r="D6" s="3">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E6" s="3">
-        <v>53.3</v>
+        <v>53.5</v>
       </c>
       <c r="F6" s="3">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="G6" s="3">
-        <v>-30.97</v>
+        <v>-27.33</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -10260,22 +10182,22 @@
         <v>3.0</v>
       </c>
       <c r="B7" s="3">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C7" s="3">
         <v>28.1</v>
       </c>
       <c r="D7" s="3">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E7" s="3">
-        <v>52.5</v>
+        <v>52.6</v>
       </c>
       <c r="F7" s="3">
-        <v>0.0</v>
+        <v>0.01</v>
       </c>
       <c r="G7" s="3">
-        <v>1.69</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -10659,22 +10581,22 @@
         <v>0.5</v>
       </c>
       <c r="B2" s="3">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="C2" s="3">
-        <v>81.9</v>
+        <v>81.8</v>
       </c>
       <c r="D2" s="3">
         <v>618</v>
       </c>
       <c r="E2" s="3">
-        <v>50.4</v>
+        <v>50.3</v>
       </c>
       <c r="F2" s="3">
         <v>0.2</v>
       </c>
       <c r="G2" s="3">
-        <v>244.25</v>
+        <v>244.03</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -10685,7 +10607,7 @@
         <v>995</v>
       </c>
       <c r="C3" s="3">
-        <v>66.4</v>
+        <v>66.3</v>
       </c>
       <c r="D3" s="3">
         <v>524</v>
@@ -10708,7 +10630,7 @@
         <v>784</v>
       </c>
       <c r="C4" s="3">
-        <v>52.3</v>
+        <v>52.2</v>
       </c>
       <c r="D4" s="3">
         <v>432</v>
@@ -11176,10 +11098,10 @@
         <v>3</v>
       </c>
       <c r="C2" s="3">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
       <c r="D2" s="3">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E2" s="3">
         <v>10</v>
@@ -11245,10 +11167,10 @@
         <v>3</v>
       </c>
       <c r="C5" s="3">
-        <v>54.4</v>
+        <v>54.2</v>
       </c>
       <c r="D5" s="3">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="E5" s="3">
         <v>15</v>
@@ -11277,10 +11199,10 @@
         <v>20</v>
       </c>
       <c r="F6" s="3">
-        <v>44.8</v>
+        <v>45.0</v>
       </c>
       <c r="G6" s="3">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
   </sheetData>
@@ -11341,16 +11263,16 @@
         </is>
       </c>
       <c r="C2" s="3">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D2" s="3">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E2" s="3">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
       <c r="F2" s="3">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -11385,16 +11307,16 @@
         </is>
       </c>
       <c r="C4" s="3">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D4" s="3">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E4" s="3">
-        <v>47.9</v>
+        <v>48.1</v>
       </c>
       <c r="F4" s="3">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -11987,16 +11909,16 @@
         </is>
       </c>
       <c r="C3" s="3">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="D3" s="3">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E3" s="3">
-        <v>45.0</v>
+        <v>45.2</v>
       </c>
       <c r="F3" s="3">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="4" spans="1:6">
